--- a/Resultados/- Resultados.xlsx
+++ b/Resultados/- Resultados.xlsx
@@ -1,27 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\Resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C02EA7-B9A0-4B2E-8902-4118FA135878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E63016B-67BD-497F-897C-A913277BC44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="9" r:id="rId1"/>
     <sheet name="MountainDatabase" sheetId="17" r:id="rId2"/>
     <sheet name="PalaceDatabase" sheetId="18" r:id="rId3"/>
     <sheet name="WashingtonDatabase" sheetId="16" r:id="rId4"/>
+    <sheet name="ParkDatabase" sheetId="19" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MountainDatabase!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ParkDatabase!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">WashingtonDatabase!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="71">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -247,13 +249,26 @@
   <si>
     <t>Alternative (30)</t>
   </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Distância Euclidiana</t>
+  </si>
+  <si>
+    <t>Distância de Manhattan</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000000000000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -412,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -467,6 +482,12 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,7 +565,7 @@
           <c:x val="6.708286735947222E-2"/>
           <c:y val="9.442161516380955E-2"/>
           <c:w val="0.92001075377594732"/>
-          <c:h val="0.70519411793005016"/>
+          <c:h val="0.60924529054121401"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1694,7 +1715,8 @@
         <c:axId val="392152351"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="17"/>
+          <c:max val="16"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1777,7 +1799,8 @@
         <c:crossAx val="392150687"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="1.5"/>
+        <c:majorUnit val="2"/>
+        <c:minorUnit val="2"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -3550,7 +3573,942 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" b="1"/>
+              <a:t>Distância de Hamming para Cada Algoritmo de Hashing entre a Imagem Original e uma Imagem Alterada</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.708286735947222E-2"/>
+          <c:y val="9.442161516380955E-2"/>
+          <c:w val="0.92001075377594732"/>
+          <c:h val="0.67973668596353376"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ParkDatabase!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>ParkDatabase!$A$3:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ParkDatabase!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9C5F-4C05-BDE1-43E87E9AEB94}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ParkDatabase!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>ParkDatabase!$A$3:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ParkDatabase!$C$3:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9C5F-4C05-BDE1-43E87E9AEB94}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ParkDatabase!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>D. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>ParkDatabase!$A$3:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ParkDatabase!$D$3:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9C5F-4C05-BDE1-43E87E9AEB94}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ParkDatabase!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>W. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>ParkDatabase!$A$3:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ParkDatabase!$E$3:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9C5F-4C05-BDE1-43E87E9AEB94}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ParkDatabase!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hsv-Color Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>ParkDatabase!$A$3:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ParkDatabase!$F$3:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9C5F-4C05-BDE1-43E87E9AEB94}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ParkDatabase!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CP Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="7030A0"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>ParkDatabase!$A$3:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ParkDatabase!$G$3:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0" formatCode="0.00">
+                  <c:v>13.77</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.44</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>6.66</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.00">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.00">
+                  <c:v>31.11</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.00">
+                  <c:v>14.4</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.00">
+                  <c:v>11.33</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.00">
+                  <c:v>26.66</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.00">
+                  <c:v>28.88</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.00">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-9C5F-4C05-BDE1-43E87E9AEB94}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="392150687"/>
+        <c:axId val="392152351"/>
+        <c:extLst/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="392150687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Imagens Alteradas</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.46941254872126892"/>
+              <c:y val="0.90560344136371651"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="392152351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="115"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="392152351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="55"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Distância</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-BR" baseline="0"/>
+                  <a:t> de Hamming </a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.9946221881624392E-2"/>
+              <c:y val="0.32089614169566544"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="392150687"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.5704766815327571E-2"/>
+          <c:y val="0.94176582369826323"/>
+          <c:w val="0.82859036688846588"/>
+          <c:h val="5.8234176301736718E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -3630,7 +4588,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>LennaDatabase!$B$50</c:f>
+              <c:f>ParkDatabase!$B$42</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3668,11 +4626,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>LennaDatabase!$A$51:$A$56</c15:sqref>
+                    <c15:sqref>ParkDatabase!$A$43:$A$48</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(LennaDatabase!$A$51:$A$54,LennaDatabase!$A$56)</c:f>
+              <c:f>(ParkDatabase!$A$43:$A$46,ParkDatabase!$A$48)</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -3698,28 +4656,28 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>LennaDatabase!$B$51:$B$56</c15:sqref>
+                    <c15:sqref>ParkDatabase!$B$43:$B$48</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(LennaDatabase!$B$51:$B$54,LennaDatabase!$B$56)</c:f>
+              <c:f>(ParkDatabase!$B$43:$B$46,ParkDatabase!$B$48)</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>24.494897427831699</c:v>
+                  <c:v>13.4164078649987</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23.664319132398401</c:v>
+                  <c:v>14.3527000944073</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17.8605710994917</c:v>
+                  <c:v>7.3484692283495301</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22.203603311174501</c:v>
+                  <c:v>8.9442719099991592</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>36.681120484521699</c:v>
+                  <c:v>75.970080294810799</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3727,7 +4685,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FF40-48B8-B418-7F6FC1EFF6D4}"/>
+              <c16:uniqueId val="{00000000-ADFC-4D1B-BBFB-CC807421F14A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3813,7 +4771,7 @@
         <c:axId val="1631798208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="40"/>
+          <c:max val="90"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -3872,7 +4830,882 @@
         <c:crossAx val="1631798624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="8"/>
+        <c:majorUnit val="15"/>
+        <c:minorUnit val="2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Manhattan Distance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ParkDatabase!$C$42</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Manhattan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>ParkDatabase!$A$43:$A$48</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(ParkDatabase!$A$43:$A$46,ParkDatabase!$A$48)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>A. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>P. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>D. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>W. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>CP Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>ParkDatabase!$C$43:$C$48</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(ParkDatabase!$C$43:$C$46,ParkDatabase!$C$48)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.00">
+                  <c:v>202.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0967-467F-8295-009C9B88DA0A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1631798624"/>
+        <c:axId val="1631798208"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1631798624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798208"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1631798208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="300"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="45"/>
+        <c:minorUnit val="2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Euclidean Distance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>LennaDatabase!$B$50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Distância Euclidiana</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>LennaDatabase!$A$51:$A$56</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(LennaDatabase!$A$51:$A$54,LennaDatabase!$A$56)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>A. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>P. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>D. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>W. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>CP Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>LennaDatabase!$B$51:$B$56</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(LennaDatabase!$B$51:$B$54,LennaDatabase!$B$56)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>24.494897427831699</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.664319132398401</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.8605710994917</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.203603311174501</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.681120484521699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FF40-48B8-B418-7F6FC1EFF6D4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1631798624"/>
+        <c:axId val="1631798208"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1631798624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798208"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1631798208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="40"/>
+          <c:min val="15"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="5"/>
         <c:minorUnit val="2"/>
       </c:valAx>
       <c:spPr>
@@ -4042,7 +5875,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Manhattan</c:v>
+                  <c:v>Distância de Manhattan</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4071,6 +5904,64 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:extLst>
@@ -4222,7 +6113,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="120"/>
-          <c:min val="0"/>
+          <c:min val="30"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -6984,6 +8875,90 @@
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7112,6 +9087,90 @@
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7240,6 +9299,90 @@
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7366,6 +9509,90 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7515,6 +9742,90 @@
                 <c:pt idx="0">
                   <c:v>6</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7657,10 +9968,94 @@
             <c:numRef>
               <c:f>PalaceDatabase!$G$3:$G$31</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="29"/>
-                <c:pt idx="0" formatCode="0.00">
+                <c:pt idx="0">
                   <c:v>15.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15.4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>15.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8072,6 +10467,21 @@
               <c:numCache>
                 <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>26.8514431641951</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27.313000567495301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.099800796022201</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>28.407745422683501</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.682041580986606</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8465,6 +10875,21 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.0">
+                  <c:v>452.8</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8703,6 +11128,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -9022,6 +11487,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -9538,7 +12043,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10054,7 +12559,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10570,7 +13075,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11086,7 +13591,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11602,7 +14107,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -12118,7 +14623,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -12634,7 +15139,1039 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13160,10 +16697,10 @@
       <xdr:rowOff>137583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>173303</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>10584</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>10583</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13198,10 +16735,10 @@
       <xdr:rowOff>14153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>328084</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>177271</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>920750</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>169333</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13230,16 +16767,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>693870</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>9263</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1043121</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>189180</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>423332</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>172381</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>709083</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13626,6 +17163,125 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>87313</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>74083</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>592667</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>109803</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74B34E7E-31AA-4CF6-A37C-9ED4D47F65B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>14153</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>328084</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>177271</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{638EF00D-C318-43B2-86BF-26C41142A771}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>693870</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>9263</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>423332</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>172381</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AD48184-55C2-4BCC-BF35-782A0FC65E94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -13928,7 +17584,7 @@
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
@@ -14424,17 +18080,17 @@
         <v>22</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B51" s="24">
         <v>24.494897427831699</v>
       </c>
       <c r="C51" s="1">
@@ -14445,7 +18101,7 @@
       <c r="A52" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="15">
+      <c r="B52" s="24">
         <v>23.664319132398401</v>
       </c>
       <c r="C52" s="1">
@@ -14456,7 +18112,7 @@
       <c r="A53" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="24">
         <v>17.8605710994917</v>
       </c>
       <c r="C53" s="1">
@@ -14467,7 +18123,7 @@
       <c r="A54" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B54" s="15">
+      <c r="B54" s="24">
         <v>22.203603311174501</v>
       </c>
       <c r="C54" s="1">
@@ -14478,7 +18134,7 @@
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B55" s="15">
+      <c r="B55" s="24">
         <v>7.2111025509279703</v>
       </c>
       <c r="C55" s="1">
@@ -14489,7 +18145,7 @@
       <c r="A56" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B56" s="15">
+      <c r="B56" s="24">
         <v>36.681120484521699</v>
       </c>
       <c r="C56" s="18">
@@ -15414,320 +19070,668 @@
       <c r="A4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
+      <c r="B4" s="21">
+        <v>0</v>
+      </c>
+      <c r="C4" s="21">
+        <v>0</v>
+      </c>
+      <c r="D4" s="21">
+        <v>2</v>
+      </c>
+      <c r="E4" s="21">
+        <v>0</v>
+      </c>
+      <c r="F4" s="21">
+        <v>3</v>
+      </c>
+      <c r="G4" s="22">
+        <v>15.4</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="22"/>
+      <c r="B5" s="21">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
+        <v>4</v>
+      </c>
+      <c r="G5" s="22">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="22"/>
+      <c r="B6" s="21">
+        <v>0</v>
+      </c>
+      <c r="C6" s="21">
+        <v>0</v>
+      </c>
+      <c r="D6" s="21">
+        <v>0</v>
+      </c>
+      <c r="E6" s="21">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21">
+        <v>4</v>
+      </c>
+      <c r="G6" s="22">
+        <v>15.4</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="22"/>
+      <c r="B7" s="21">
+        <v>0</v>
+      </c>
+      <c r="C7" s="21">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21">
+        <v>0</v>
+      </c>
+      <c r="E7" s="21">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <v>4</v>
+      </c>
+      <c r="G7" s="22">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="22"/>
+      <c r="B8" s="21">
+        <v>0</v>
+      </c>
+      <c r="C8" s="21">
+        <v>0</v>
+      </c>
+      <c r="D8" s="21">
+        <v>2</v>
+      </c>
+      <c r="E8" s="21">
+        <v>0</v>
+      </c>
+      <c r="F8" s="21">
+        <v>4</v>
+      </c>
+      <c r="G8" s="22">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="22"/>
+      <c r="B9" s="21">
+        <v>0</v>
+      </c>
+      <c r="C9" s="21">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21">
+        <v>1</v>
+      </c>
+      <c r="E9" s="21">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21">
+        <v>5</v>
+      </c>
+      <c r="G9" s="22">
+        <v>15.4</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="22"/>
+      <c r="B10" s="21">
+        <v>0</v>
+      </c>
+      <c r="C10" s="21">
+        <v>0</v>
+      </c>
+      <c r="D10" s="21">
+        <v>1</v>
+      </c>
+      <c r="E10" s="21">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21">
+        <v>4</v>
+      </c>
+      <c r="G10" s="22">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="22"/>
+      <c r="B11" s="21">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <v>3</v>
+      </c>
+      <c r="G11" s="22">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
+      <c r="B12" s="21">
+        <v>0</v>
+      </c>
+      <c r="C12" s="20">
+        <v>0</v>
+      </c>
+      <c r="D12" s="20">
+        <v>2</v>
+      </c>
+      <c r="E12" s="20">
+        <v>0</v>
+      </c>
+      <c r="F12" s="21">
+        <v>4</v>
+      </c>
+      <c r="G12" s="22">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
+      <c r="B13" s="21">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21">
+        <v>2</v>
+      </c>
+      <c r="E13" s="21">
+        <v>0</v>
+      </c>
+      <c r="F13" s="21">
+        <v>4</v>
+      </c>
+      <c r="G13" s="22">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="22"/>
+      <c r="B14" s="21">
+        <v>0</v>
+      </c>
+      <c r="C14" s="21">
+        <v>0</v>
+      </c>
+      <c r="D14" s="21">
+        <v>2</v>
+      </c>
+      <c r="E14" s="21">
+        <v>0</v>
+      </c>
+      <c r="F14" s="21">
+        <v>4</v>
+      </c>
+      <c r="G14" s="22">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="22"/>
+      <c r="B15" s="21">
+        <v>0</v>
+      </c>
+      <c r="C15" s="21">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21">
+        <v>0</v>
+      </c>
+      <c r="E15" s="21">
+        <v>0</v>
+      </c>
+      <c r="F15" s="21">
+        <v>3</v>
+      </c>
+      <c r="G15" s="22">
+        <v>15</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="22"/>
+      <c r="B16" s="21">
+        <v>0</v>
+      </c>
+      <c r="C16" s="20">
+        <v>2</v>
+      </c>
+      <c r="D16" s="20">
+        <v>2</v>
+      </c>
+      <c r="E16" s="20">
+        <v>0</v>
+      </c>
+      <c r="F16" s="20">
+        <v>5</v>
+      </c>
+      <c r="G16" s="22">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
+      <c r="B17" s="21">
+        <v>0</v>
+      </c>
+      <c r="C17" s="21">
+        <v>0</v>
+      </c>
+      <c r="D17" s="21">
+        <v>1</v>
+      </c>
+      <c r="E17" s="21">
+        <v>0</v>
+      </c>
+      <c r="F17" s="21">
+        <v>4</v>
+      </c>
+      <c r="G17" s="22">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="22"/>
+      <c r="B18" s="21">
+        <v>0</v>
+      </c>
+      <c r="C18" s="21">
+        <v>0</v>
+      </c>
+      <c r="D18" s="21">
+        <v>1</v>
+      </c>
+      <c r="E18" s="21">
+        <v>0</v>
+      </c>
+      <c r="F18" s="21">
+        <v>4</v>
+      </c>
+      <c r="G18" s="22">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22"/>
+      <c r="B19" s="21">
+        <v>10</v>
+      </c>
+      <c r="C19" s="21">
+        <v>10</v>
+      </c>
+      <c r="D19" s="21">
+        <v>10</v>
+      </c>
+      <c r="E19" s="21">
+        <v>11</v>
+      </c>
+      <c r="F19" s="21">
+        <v>4</v>
+      </c>
+      <c r="G19" s="22">
+        <v>15.4</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
+      <c r="B20" s="21">
+        <v>10</v>
+      </c>
+      <c r="C20" s="21">
+        <v>11</v>
+      </c>
+      <c r="D20" s="21">
+        <v>9</v>
+      </c>
+      <c r="E20" s="21">
+        <v>11</v>
+      </c>
+      <c r="F20" s="21">
+        <v>2</v>
+      </c>
+      <c r="G20" s="22">
+        <v>15.4</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="19"/>
+      <c r="B21" s="1">
+        <v>10</v>
+      </c>
+      <c r="C21" s="1">
+        <v>10</v>
+      </c>
+      <c r="D21" s="1">
+        <v>10</v>
+      </c>
+      <c r="E21" s="1">
+        <v>11</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="19">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="19"/>
+      <c r="B22" s="1">
+        <v>11</v>
+      </c>
+      <c r="C22" s="1">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1">
+        <v>8</v>
+      </c>
+      <c r="E22" s="1">
+        <v>9</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="19">
+        <v>14.8</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="19"/>
+      <c r="B23" s="1">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1">
+        <v>10</v>
+      </c>
+      <c r="D23" s="1">
+        <v>9</v>
+      </c>
+      <c r="E23" s="1">
+        <v>11</v>
+      </c>
+      <c r="F23" s="1">
+        <v>4</v>
+      </c>
+      <c r="G23" s="19">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="19"/>
+      <c r="B24" s="1">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1">
+        <v>9</v>
+      </c>
+      <c r="E24" s="1">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3</v>
+      </c>
+      <c r="G24" s="19">
+        <v>15</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="19"/>
+      <c r="B25" s="1">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1">
+        <v>10</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9</v>
+      </c>
+      <c r="E25" s="1">
+        <v>11</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2</v>
+      </c>
+      <c r="G25" s="19">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="19"/>
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>4</v>
+      </c>
+      <c r="G26" s="19">
+        <v>15</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="19"/>
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2</v>
+      </c>
+      <c r="G27" s="19">
+        <v>15</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="19"/>
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>4</v>
+      </c>
+      <c r="G28" s="19">
+        <v>15</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="19"/>
+      <c r="B29" s="1">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1">
+        <v>4</v>
+      </c>
+      <c r="G29" s="19">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="19"/>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1">
+        <v>3</v>
+      </c>
+      <c r="G30" s="19">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="19"/>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>4</v>
+      </c>
+      <c r="G31" s="19">
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="19"/>
+      <c r="B32" s="1">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1">
+        <v>3</v>
+      </c>
+      <c r="G32" s="19">
+        <v>15</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
@@ -15744,43 +19748,67 @@
       <c r="A62" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="1"/>
+      <c r="B62" s="15">
+        <v>26.8514431641951</v>
+      </c>
+      <c r="C62" s="1">
+        <v>71</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="1"/>
+      <c r="B63" s="15">
+        <v>27.313000567495301</v>
+      </c>
+      <c r="C63" s="1">
+        <v>74</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B64" s="15"/>
-      <c r="C64" s="1"/>
+      <c r="B64" s="15">
+        <v>25.099800796022201</v>
+      </c>
+      <c r="C64" s="1">
+        <v>90</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="1"/>
+      <c r="B65" s="15">
+        <v>28.407745422683501</v>
+      </c>
+      <c r="C65" s="1">
+        <v>75</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="1"/>
+      <c r="B66" s="15">
+        <v>20.5182845286831</v>
+      </c>
+      <c r="C66" s="1">
+        <v>109</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="18"/>
+      <c r="B67" s="15">
+        <v>82.682041580986606</v>
+      </c>
+      <c r="C67" s="23">
+        <v>452.8</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
@@ -16080,4 +20108,384 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DE05E8F-84CF-464F-9851-002DD2A6D98C}">
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="21">
+        <v>0</v>
+      </c>
+      <c r="D3" s="21">
+        <v>0</v>
+      </c>
+      <c r="E3" s="21">
+        <v>0</v>
+      </c>
+      <c r="F3" s="21">
+        <v>1</v>
+      </c>
+      <c r="G3" s="22">
+        <v>13.77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="21">
+        <v>0</v>
+      </c>
+      <c r="D4" s="21">
+        <v>0</v>
+      </c>
+      <c r="E4" s="21">
+        <v>0</v>
+      </c>
+      <c r="F4" s="21">
+        <v>1</v>
+      </c>
+      <c r="G4" s="21">
+        <v>9.44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="21">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21">
+        <v>0</v>
+      </c>
+      <c r="E5" s="21">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="21">
+        <v>0</v>
+      </c>
+      <c r="D6" s="21">
+        <v>1</v>
+      </c>
+      <c r="E6" s="21">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21">
+        <v>1</v>
+      </c>
+      <c r="G6" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="21">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <v>1</v>
+      </c>
+      <c r="G7" s="22">
+        <v>31.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="21">
+        <v>6</v>
+      </c>
+      <c r="C8" s="21">
+        <v>6</v>
+      </c>
+      <c r="D8" s="21">
+        <v>3</v>
+      </c>
+      <c r="E8" s="21">
+        <v>4</v>
+      </c>
+      <c r="F8" s="21">
+        <v>0</v>
+      </c>
+      <c r="G8" s="22">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="21">
+        <v>6</v>
+      </c>
+      <c r="D9" s="21">
+        <v>3</v>
+      </c>
+      <c r="E9" s="21">
+        <v>4</v>
+      </c>
+      <c r="F9" s="21">
+        <v>1</v>
+      </c>
+      <c r="G9" s="22">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="21">
+        <v>7</v>
+      </c>
+      <c r="D10" s="21">
+        <v>3</v>
+      </c>
+      <c r="E10" s="21">
+        <v>4</v>
+      </c>
+      <c r="F10" s="21">
+        <v>0</v>
+      </c>
+      <c r="G10" s="22">
+        <v>26.66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="21">
+        <v>6</v>
+      </c>
+      <c r="D11" s="21">
+        <v>3</v>
+      </c>
+      <c r="E11" s="21">
+        <v>4</v>
+      </c>
+      <c r="F11" s="21">
+        <v>1</v>
+      </c>
+      <c r="G11" s="22">
+        <v>28.88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="20">
+        <v>7</v>
+      </c>
+      <c r="D12" s="20">
+        <v>4</v>
+      </c>
+      <c r="E12" s="20">
+        <v>4</v>
+      </c>
+      <c r="F12" s="21">
+        <v>1</v>
+      </c>
+      <c r="G12" s="22">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="15">
+        <v>13.4164078649987</v>
+      </c>
+      <c r="C43" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="15">
+        <v>14.3527000944073</v>
+      </c>
+      <c r="C44" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" s="15">
+        <v>7.3484692283495301</v>
+      </c>
+      <c r="C45" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="15">
+        <v>8.9442719099991592</v>
+      </c>
+      <c r="C46" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" s="15">
+        <v>2.6457513110645898</v>
+      </c>
+      <c r="C47" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" s="15">
+        <v>75.970080294810799</v>
+      </c>
+      <c r="C48" s="24">
+        <v>202.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G12" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G12">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Resultados/- Resultados.xlsx
+++ b/Resultados/- Resultados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\Resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E63016B-67BD-497F-897C-A913277BC44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23FF86C-2E79-418D-A92A-B7F24E819EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="9" r:id="rId1"/>
